--- a/GradeSession_1_Dec/StudentsSolution.xlsx
+++ b/GradeSession_1_Dec/StudentsSolution.xlsx
@@ -46,10 +46,10 @@
     <x:t>Success</x:t>
   </x:si>
   <x:si>
-    <x:t>01-12-2025 01:17:36</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01-12-2025 01:18:54</x:t>
+    <x:t>01-12-2025 03:15:12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01-12-2025 03:15:59</x:t>
   </x:si>
   <x:si>
     <x:t>2</x:t>
@@ -58,25 +58,19 @@
     <x:t>dongnvhe172649</x:t>
   </x:si>
   <x:si>
+    <x:t>01-12-2025 03:16:52</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hoangbsthe186345</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01-12-2025 03:17:45</x:t>
+  </x:si>
+  <x:si>
     <x:t>4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01-12-2025 01:18:55</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01-12-2025 01:19:57</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hoangbsthe186345</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01-12-2025 01:19:58</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01-12-2025 01:21:02</x:t>
   </x:si>
   <x:si>
     <x:t>Not Run</x:t>
@@ -557,21 +551,21 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="E3" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="F3" s="2" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G3" s="2" t="s">
         <x:v>14</x:v>
-      </x:c>
-      <x:c r="F3" s="2" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G3" s="2" t="s">
-        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:7">
       <x:c r="A4" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B4" s="2" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C4" s="2" t="s">
         <x:v>7</x:v>
@@ -580,18 +574,18 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="E4" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="F4" s="2" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="F4" s="2" t="s">
-        <x:v>19</x:v>
-      </x:c>
       <x:c r="G4" s="2" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:7">
       <x:c r="A5" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>8</x:v>
@@ -600,21 +594,21 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:7">
       <x:c r="A6" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>13</x:v>
@@ -623,85 +617,85 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:7">
       <x:c r="A7" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:7">
       <x:c r="A8" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:7">
       <x:c r="A9" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/GradeSession_1_Dec/StudentsSolution.xlsx
+++ b/GradeSession_1_Dec/StudentsSolution.xlsx
@@ -46,10 +46,10 @@
     <x:t>Success</x:t>
   </x:si>
   <x:si>
-    <x:t>01-12-2025 03:15:12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01-12-2025 03:15:59</x:t>
+    <x:t>01-12-2025 10:00:37</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01-12-2025 10:01:28</x:t>
   </x:si>
   <x:si>
     <x:t>2</x:t>
@@ -58,7 +58,10 @@
     <x:t>dongnvhe172649</x:t>
   </x:si>
   <x:si>
-    <x:t>01-12-2025 03:16:52</x:t>
+    <x:t>01-12-2025 10:01:29</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01-12-2025 10:02:31</x:t>
   </x:si>
   <x:si>
     <x:t>3</x:t>
@@ -67,7 +70,10 @@
     <x:t>hoangbsthe186345</x:t>
   </x:si>
   <x:si>
-    <x:t>01-12-2025 03:17:45</x:t>
+    <x:t>01-12-2025 10:02:32</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01-12-2025 10:03:31</x:t>
   </x:si>
   <x:si>
     <x:t>4</x:t>
@@ -554,18 +560,18 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="F3" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G3" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:7">
       <x:c r="A4" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B4" s="2" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C4" s="2" t="s">
         <x:v>7</x:v>
@@ -577,15 +583,15 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="F4" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G4" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:7">
       <x:c r="A5" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>8</x:v>
@@ -594,21 +600,21 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:7">
       <x:c r="A6" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>13</x:v>
@@ -617,85 +623,85 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:7">
       <x:c r="A7" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:7">
       <x:c r="A8" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:7">
       <x:c r="A9" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/GradeSession_1_Dec/StudentsSolution.xlsx
+++ b/GradeSession_1_Dec/StudentsSolution.xlsx
@@ -46,10 +46,13 @@
     <x:t>Success</x:t>
   </x:si>
   <x:si>
-    <x:t>01-12-2025 10:00:37</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01-12-2025 10:01:28</x:t>
+    <x:t>0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01-12-2025 10:13:26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01-12-2025 10:14:08</x:t>
   </x:si>
   <x:si>
     <x:t>2</x:t>
@@ -58,10 +61,7 @@
     <x:t>dongnvhe172649</x:t>
   </x:si>
   <x:si>
-    <x:t>01-12-2025 10:01:29</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01-12-2025 10:02:31</x:t>
+    <x:t>01-12-2025 10:14:50</x:t>
   </x:si>
   <x:si>
     <x:t>3</x:t>
@@ -70,19 +70,13 @@
     <x:t>hoangbsthe186345</x:t>
   </x:si>
   <x:si>
-    <x:t>01-12-2025 10:02:32</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01-12-2025 10:03:31</x:t>
+    <x:t>01-12-2025 10:15:32</x:t>
   </x:si>
   <x:si>
     <x:t>4</x:t>
   </x:si>
   <x:si>
     <x:t>Not Run</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0</x:t>
   </x:si>
   <x:si>
     <x:t/>
@@ -534,21 +528,21 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="E2" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F2" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G2" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:7">
       <x:c r="A3" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C3" s="2" t="s">
         <x:v>7</x:v>
@@ -557,10 +551,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="E3" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F3" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G3" s="2" t="s">
         <x:v>15</x:v>
@@ -580,128 +574,128 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="E4" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F4" s="2" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G4" s="2" t="s">
         <x:v>18</x:v>
-      </x:c>
-      <x:c r="G4" s="2" t="s">
-        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:7">
       <x:c r="A5" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:7">
       <x:c r="A6" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C6" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:7">
       <x:c r="A7" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:7">
       <x:c r="A8" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:7">
       <x:c r="A9" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/GradeSession_1_Dec/StudentsSolution.xlsx
+++ b/GradeSession_1_Dec/StudentsSolution.xlsx
@@ -46,22 +46,25 @@
     <x:t>Success</x:t>
   </x:si>
   <x:si>
+    <x:t>01-12-2025 10:25:43</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01-12-2025 10:26:36</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dongnvhe172649</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Not Run</x:t>
+  </x:si>
+  <x:si>
     <x:t>0</x:t>
   </x:si>
   <x:si>
-    <x:t>01-12-2025 10:13:26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01-12-2025 10:14:08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dongnvhe172649</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01-12-2025 10:14:50</x:t>
+    <x:t/>
   </x:si>
   <x:si>
     <x:t>3</x:t>
@@ -70,16 +73,7 @@
     <x:t>hoangbsthe186345</x:t>
   </x:si>
   <x:si>
-    <x:t>01-12-2025 10:15:32</x:t>
-  </x:si>
-  <x:si>
     <x:t>4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Not Run</x:t>
-  </x:si>
-  <x:si>
-    <x:t/>
   </x:si>
   <x:si>
     <x:t>5</x:t>
@@ -528,59 +522,59 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="E2" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="F2" s="2" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F2" s="2" t="s">
+      <x:c r="G2" s="2" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="G2" s="2" t="s">
+    </x:row>
+    <x:row r="3" spans="1:7">
+      <x:c r="A3" s="0" t="s">
         <x:v>12</x:v>
       </x:c>
-    </x:row>
-    <x:row r="3" spans="1:7">
-      <x:c r="A3" s="2" t="s">
+      <x:c r="B3" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B3" s="2" t="s">
+      <x:c r="C3" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s">
+      <x:c r="E3" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:7">
+      <x:c r="A4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D3" s="2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="E3" s="2" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F3" s="2" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G3" s="2" t="s">
+      <x:c r="D4" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E4" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
-    </x:row>
-    <x:row r="4" spans="1:7">
-      <x:c r="A4" s="2" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="B4" s="2" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C4" s="2" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D4" s="2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="E4" s="2" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F4" s="2" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G4" s="2" t="s">
-        <x:v>18</x:v>
+      <x:c r="F4" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G4" s="0" t="s">
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:7">
@@ -591,111 +585,111 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:7">
       <x:c r="A6" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C6" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D6" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:7">
       <x:c r="A7" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:7">
       <x:c r="A8" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:7">
       <x:c r="A9" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/GradeSession_1_Dec/StudentsSolution.xlsx
+++ b/GradeSession_1_Dec/StudentsSolution.xlsx
@@ -43,13 +43,16 @@
     <x:t>cuongnhhe186494</x:t>
   </x:si>
   <x:si>
-    <x:t>Success</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01-12-2025 10:25:43</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01-12-2025 10:26:36</x:t>
+    <x:t>Failed</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01-12-2025 10:50:49</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01-12-2025 10:51:58</x:t>
   </x:si>
   <x:si>
     <x:t>2</x:t>
@@ -59,9 +62,6 @@
   </x:si>
   <x:si>
     <x:t>Not Run</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0</x:t>
   </x:si>
   <x:si>
     <x:t/>
@@ -132,7 +132,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF90EE90"/>
+        <x:fgColor rgb="FFFFB6C1"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -522,30 +522,30 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="E2" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F2" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G2" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:7">
       <x:c r="A3" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
         <x:v>16</x:v>
@@ -565,10 +565,10 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
         <x:v>16</x:v>
@@ -585,13 +585,13 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
         <x:v>16</x:v>
@@ -605,16 +605,16 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C6" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
         <x:v>16</x:v>
@@ -631,13 +631,13 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
         <x:v>16</x:v>
@@ -654,13 +654,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
         <x:v>16</x:v>
@@ -677,13 +677,13 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
         <x:v>16</x:v>

--- a/GradeSession_1_Dec/StudentsSolution.xlsx
+++ b/GradeSession_1_Dec/StudentsSolution.xlsx
@@ -46,10 +46,13 @@
     <x:t>Success</x:t>
   </x:si>
   <x:si>
-    <x:t>01-12-2025 03:15:12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01-12-2025 03:15:59</x:t>
+    <x:t>0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02-12-2025 12:32:53</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02-12-2025 12:34:41</x:t>
   </x:si>
   <x:si>
     <x:t>2</x:t>
@@ -58,7 +61,10 @@
     <x:t>dongnvhe172649</x:t>
   </x:si>
   <x:si>
-    <x:t>01-12-2025 03:16:52</x:t>
+    <x:t>Not Run</x:t>
+  </x:si>
+  <x:si>
+    <x:t/>
   </x:si>
   <x:si>
     <x:t>3</x:t>
@@ -67,19 +73,7 @@
     <x:t>hoangbsthe186345</x:t>
   </x:si>
   <x:si>
-    <x:t>01-12-2025 03:17:45</x:t>
-  </x:si>
-  <x:si>
     <x:t>4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Not Run</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0</x:t>
-  </x:si>
-  <x:si>
-    <x:t/>
   </x:si>
   <x:si>
     <x:t>5</x:t>
@@ -528,174 +522,174 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="E2" s="2" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F2" s="2" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G2" s="2" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:7">
+      <x:c r="A3" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="F2" s="2" t="s">
+      <x:c r="D3" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="G2" s="2" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:7">
-      <x:c r="A3" s="2" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="B3" s="2" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="C3" s="2" t="s">
+      <x:c r="F3" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:7">
+      <x:c r="A4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D3" s="2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="E3" s="2" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="F3" s="2" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G3" s="2" t="s">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:7">
-      <x:c r="A4" s="2" t="s">
+      <x:c r="D4" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="B4" s="2" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C4" s="2" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D4" s="2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="E4" s="2" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="F4" s="2" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="G4" s="2" t="s">
-        <x:v>17</x:v>
+      <x:c r="E4" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F4" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G4" s="0" t="s">
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:7">
       <x:c r="A5" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:7">
       <x:c r="A6" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C6" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:7">
       <x:c r="A7" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:7">
       <x:c r="A8" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:7">
       <x:c r="A9" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/GradeSession_1_Dec/StudentsSolution.xlsx
+++ b/GradeSession_1_Dec/StudentsSolution.xlsx
@@ -46,34 +46,46 @@
     <x:t>Success</x:t>
   </x:si>
   <x:si>
+    <x:t>02-12-2025 13:44:58</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02-12-2025 13:46:24</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dongnvhe172649</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02-12-2025 13:46:25</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02-12-2025 13:47:35</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hoangbsthe186345</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02-12-2025 13:47:36</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02-12-2025 13:48:46</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Not Run</x:t>
+  </x:si>
+  <x:si>
     <x:t>0</x:t>
   </x:si>
   <x:si>
-    <x:t>02-12-2025 12:32:53</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02-12-2025 12:34:41</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dongnvhe172649</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Not Run</x:t>
-  </x:si>
-  <x:si>
     <x:t/>
-  </x:si>
-  <x:si>
-    <x:t>3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hoangbsthe186345</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4</x:t>
   </x:si>
   <x:si>
     <x:t>5</x:t>
@@ -522,174 +534,174 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="E2" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="F2" s="2" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F2" s="2" t="s">
+      <x:c r="G2" s="2" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="G2" s="2" t="s">
+    </x:row>
+    <x:row r="3" spans="1:7">
+      <x:c r="A3" s="2" t="s">
         <x:v>12</x:v>
       </x:c>
-    </x:row>
-    <x:row r="3" spans="1:7">
-      <x:c r="A3" s="0" t="s">
+      <x:c r="B3" s="2" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B3" s="0" t="s">
+      <x:c r="C3" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D3" s="2" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E3" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="F3" s="2" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C3" s="0" t="s">
+      <x:c r="G3" s="2" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:7">
+      <x:c r="A4" s="2" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B4" s="2" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C4" s="2" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D3" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E3" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F3" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G3" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:7">
-      <x:c r="A4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="B4" s="0" t="s">
+      <x:c r="D4" s="2" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E4" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="F4" s="2" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="C4" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D4" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E4" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F4" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G4" s="0" t="s">
-        <x:v>16</x:v>
+      <x:c r="G4" s="2" t="s">
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:7">
       <x:c r="A5" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>8</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:7">
       <x:c r="A6" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:7">
       <x:c r="A7" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="B7" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C7" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D7" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:7">
       <x:c r="A8" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C8" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E8" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="B8" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C8" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D8" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E8" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:7">
       <x:c r="A9" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/GradeSession_1_Dec/StudentsSolution.xlsx
+++ b/GradeSession_1_Dec/StudentsSolution.xlsx
@@ -46,10 +46,10 @@
     <x:t>Success</x:t>
   </x:si>
   <x:si>
-    <x:t>02-12-2025 13:44:58</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02-12-2025 13:46:24</x:t>
+    <x:t>02-12-2025 15:50:10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02-12-2025 15:51:46</x:t>
   </x:si>
   <x:si>
     <x:t>2</x:t>
@@ -58,10 +58,13 @@
     <x:t>dongnvhe172649</x:t>
   </x:si>
   <x:si>
-    <x:t>02-12-2025 13:46:25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02-12-2025 13:47:35</x:t>
+    <x:t>Not Run</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0</x:t>
+  </x:si>
+  <x:si>
+    <x:t/>
   </x:si>
   <x:si>
     <x:t>3</x:t>
@@ -70,22 +73,7 @@
     <x:t>hoangbsthe186345</x:t>
   </x:si>
   <x:si>
-    <x:t>02-12-2025 13:47:36</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02-12-2025 13:48:46</x:t>
-  </x:si>
-  <x:si>
     <x:t>4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Not Run</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0</x:t>
-  </x:si>
-  <x:si>
-    <x:t/>
   </x:si>
   <x:si>
     <x:t>5</x:t>
@@ -544,54 +532,54 @@
       </x:c>
     </x:row>
     <x:row r="3" spans="1:7">
-      <x:c r="A3" s="2" t="s">
+      <x:c r="A3" s="0" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="B3" s="2" t="s">
+      <x:c r="B3" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C3" s="2" t="s">
+      <x:c r="C3" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D3" s="2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="E3" s="2" t="s">
+      <x:c r="D3" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:7">
+      <x:c r="A4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="F3" s="2" t="s">
+      <x:c r="D4" s="0" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="G3" s="2" t="s">
+      <x:c r="E4" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
-    </x:row>
-    <x:row r="4" spans="1:7">
-      <x:c r="A4" s="2" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="B4" s="2" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C4" s="2" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D4" s="2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="E4" s="2" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="F4" s="2" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="G4" s="2" t="s">
-        <x:v>19</x:v>
+      <x:c r="F4" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G4" s="0" t="s">
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:7">
       <x:c r="A5" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
         <x:v>8</x:v>
@@ -600,21 +588,21 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:7">
       <x:c r="A6" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
         <x:v>13</x:v>
@@ -623,85 +611,85 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:7">
       <x:c r="A7" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:7">
       <x:c r="A8" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:7">
       <x:c r="A9" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
         <x:v>12</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/GradeSession_1_Dec/StudentsSolution.xlsx
+++ b/GradeSession_1_Dec/StudentsSolution.xlsx
@@ -46,10 +46,10 @@
     <x:t>Success</x:t>
   </x:si>
   <x:si>
-    <x:t>02-12-2025 15:50:10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02-12-2025 15:51:46</x:t>
+    <x:t>02-12-2025 21:01:38</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02-12-2025 21:03:32</x:t>
   </x:si>
   <x:si>
     <x:t>2</x:t>
